--- a/public/results/2025 Handicaps.xlsx
+++ b/public/results/2025 Handicaps.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\CODE\golf-league-site\public\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB3C7A1D-82F7-4664-8E34-105D5C098E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1076D373-45B0-4337-8668-2F9E4E6584AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5910" yWindow="240" windowWidth="19830" windowHeight="10785" xr2:uid="{5DAE91F2-6632-4C8A-97CE-8A27868A4A99}"/>
+    <workbookView xWindow="270" yWindow="105" windowWidth="19830" windowHeight="10785" xr2:uid="{5DAE91F2-6632-4C8A-97CE-8A27868A4A99}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="42">
   <si>
     <t>PLAYERS</t>
   </si>
@@ -548,7 +548,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
@@ -570,6 +570,30 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -596,39 +620,12 @@
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -646,76 +643,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1054,37 +981,37 @@
   <cols>
     <col min="3" max="3" width="10.42578125" customWidth="1"/>
     <col min="4" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="22" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="19" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="27" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="15"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
+      <c r="A2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="20"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="28"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -1096,10 +1023,10 @@
       <c r="C4" s="7">
         <v>1</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="14">
         <v>2</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="18">
         <f>C4-D4</f>
         <v>-1</v>
       </c>
@@ -1114,11 +1041,11 @@
       <c r="C5" s="8">
         <v>11</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="15">
         <v>15</v>
       </c>
-      <c r="E5" s="28">
-        <f t="shared" ref="E5:E26" si="0">C5-D5</f>
+      <c r="E5" s="19">
+        <f t="shared" ref="E5:E20" si="0">C5-D5</f>
         <v>-4</v>
       </c>
     </row>
@@ -1132,10 +1059,10 @@
       <c r="C6" s="8">
         <v>6</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="15">
         <v>8</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="19">
         <f t="shared" si="0"/>
         <v>-2</v>
       </c>
@@ -1150,8 +1077,10 @@
       <c r="C7" s="8">
         <v>6</v>
       </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="29"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="9" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
@@ -1163,10 +1092,10 @@
       <c r="C8" s="8">
         <v>11</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="15">
         <v>13</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="19">
         <f t="shared" si="0"/>
         <v>-2</v>
       </c>
@@ -1181,10 +1110,10 @@
       <c r="C9" s="8">
         <v>12</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="15">
         <v>15</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="19">
         <f t="shared" si="0"/>
         <v>-3</v>
       </c>
@@ -1199,10 +1128,10 @@
       <c r="C10" s="8">
         <v>12</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="15">
         <v>11</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="19">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -1217,10 +1146,10 @@
       <c r="C11" s="8">
         <v>15</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="15">
         <v>15</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1235,10 +1164,10 @@
       <c r="C12" s="8">
         <v>9</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="15">
         <v>8</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="19">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -1253,10 +1182,10 @@
       <c r="C13" s="8">
         <v>18</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="15">
         <v>17</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="19">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -1271,10 +1200,10 @@
       <c r="C14" s="8">
         <v>13</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="15">
         <v>13</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1289,7 +1218,7 @@
       <c r="C15" s="8">
         <v>10</v>
       </c>
-      <c r="D15" s="24"/>
+      <c r="D15" s="15"/>
       <c r="E15" s="9" t="s">
         <v>41</v>
       </c>
@@ -1304,7 +1233,7 @@
       <c r="C16" s="8">
         <v>11</v>
       </c>
-      <c r="D16" s="24"/>
+      <c r="D16" s="15"/>
       <c r="E16" s="9" t="s">
         <v>41</v>
       </c>
@@ -1319,10 +1248,10 @@
       <c r="C17" s="8">
         <v>23</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="15">
         <v>21</v>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="19">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1337,10 +1266,10 @@
       <c r="C18" s="8">
         <v>17</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="15">
         <v>22</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="20">
         <f t="shared" si="0"/>
         <v>-5</v>
       </c>
@@ -1355,7 +1284,7 @@
       <c r="C19" s="8">
         <v>14</v>
       </c>
-      <c r="D19" s="24"/>
+      <c r="D19" s="15"/>
       <c r="E19" s="9" t="s">
         <v>41</v>
       </c>
@@ -1370,10 +1299,10 @@
       <c r="C20" s="8">
         <v>22</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="15">
         <v>22</v>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1388,7 +1317,7 @@
       <c r="C21" s="8">
         <v>18</v>
       </c>
-      <c r="D21" s="24"/>
+      <c r="D21" s="15"/>
       <c r="E21" s="9" t="s">
         <v>41</v>
       </c>
@@ -1401,7 +1330,7 @@
         <v>34</v>
       </c>
       <c r="C22" s="9"/>
-      <c r="D22" s="25"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="9" t="s">
         <v>41</v>
       </c>
@@ -1414,7 +1343,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="9"/>
-      <c r="D23" s="25"/>
+      <c r="D23" s="16"/>
       <c r="E23" s="9" t="s">
         <v>41</v>
       </c>
@@ -1427,7 +1356,7 @@
         <v>36</v>
       </c>
       <c r="C24" s="9"/>
-      <c r="D24" s="25"/>
+      <c r="D24" s="16"/>
       <c r="E24" s="9" t="s">
         <v>41</v>
       </c>
@@ -1440,7 +1369,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="9"/>
-      <c r="D25" s="25"/>
+      <c r="D25" s="16"/>
       <c r="E25" s="9" t="s">
         <v>41</v>
       </c>
@@ -1453,7 +1382,7 @@
         <v>37</v>
       </c>
       <c r="C26" s="10"/>
-      <c r="D26" s="26"/>
+      <c r="D26" s="17"/>
       <c r="E26" s="10" t="s">
         <v>41</v>
       </c>
@@ -1465,11 +1394,11 @@
     <mergeCell ref="D1:D3"/>
     <mergeCell ref="E1:E3"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4:E14 E17:E18 E20">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+  <conditionalFormatting sqref="E4:E6 E17:E18 E20 E8:E14">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
